--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39CACA7-18DD-864A-AE1F-44F11034BF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0964D0EF-9D59-7E45-A494-E43057DF82C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20360" yWindow="7680" windowWidth="51200" windowHeight="26960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="38700" windowHeight="23060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_Board1_Schematic1_2026-06-0" sheetId="1" r:id="rId1"/>
@@ -44,18 +44,12 @@
     <t>1</t>
   </si>
   <si>
-    <t>1uF</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
     <t>C3216</t>
   </si>
   <si>
-    <t>25MU105MA23216</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -143,9 +137,6 @@
     <t>Ice Blue 0603</t>
   </si>
   <si>
-    <t>Rubycon</t>
-  </si>
-  <si>
     <t>HCTL</t>
   </si>
   <si>
@@ -153,6 +144,15 @@
   </si>
   <si>
     <t>cjiang</t>
+  </si>
+  <si>
+    <t>TR3A106K010C0900</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>Vishay</t>
   </si>
 </sst>
 </file>
@@ -569,177 +569,177 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
       <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>34</v>
-      </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
         <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
